--- a/01-projetos/01-data-project-foundations/data/input/absenteeism_data_29.xlsx
+++ b/01-projetos/01-data-project-foundations/data/input/absenteeism_data_29.xlsx
@@ -471,40 +471,40 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>32418</v>
+        <v>3710</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dra. Sophie Fernandes</t>
+          <t>João Felipe Viana</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>P&amp;D</t>
+          <t>Atendimento ao Cliente</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Viagem de negócios</t>
+          <t>Doença</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>45081</v>
+        <v>45080</v>
       </c>
       <c r="G2" t="n">
-        <v>10623.62</v>
+        <v>5719.59</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>81845</v>
+        <v>429</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Evelyn Barbosa</t>
+          <t>Vitor Novaes</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -514,55 +514,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45080</v>
+        <v>45079</v>
       </c>
       <c r="G3" t="n">
-        <v>5450.52</v>
+        <v>4766.93</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>81336</v>
+        <v>69536</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Luana Peixoto</t>
+          <t>Luiz Otávio Ribeiro</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>Atendimento ao Cliente</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>45078</v>
+        <v>45091</v>
       </c>
       <c r="G4" t="n">
-        <v>9537.33</v>
+        <v>7160.48</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>81340</v>
+        <v>81650</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Raul Mendes</t>
+          <t>Mariana da Conceição</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45083</v>
+        <v>45102</v>
       </c>
       <c r="G5" t="n">
-        <v>7677.22</v>
+        <v>8959.379999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>17944</v>
+        <v>42537</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Clarice das Neves</t>
+          <t>Dr. Luiz Gustavo Duarte</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -601,118 +601,118 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45093</v>
+        <v>45092</v>
       </c>
       <c r="G6" t="n">
-        <v>4250.79</v>
+        <v>6322.91</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>38226</v>
+        <v>284</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Noah Farias</t>
+          <t>Dr. Davi Lucas Monteiro</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Engenharia</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45092</v>
+        <v>45090</v>
       </c>
       <c r="G7" t="n">
-        <v>6580.79</v>
+        <v>11099.46</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>897</v>
+        <v>17361</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Caio Souza</t>
+          <t>Isabelly Gonçalves</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jurídico</t>
+          <t>Operações</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45098</v>
+        <v>45093</v>
       </c>
       <c r="G8" t="n">
-        <v>4393.48</v>
+        <v>8365.309999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>98845</v>
+        <v>54755</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sarah da Paz</t>
+          <t>Sr. Thiago Farias</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>P&amp;D</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45103</v>
+        <v>45089</v>
       </c>
       <c r="G9" t="n">
-        <v>6110.94</v>
+        <v>7723.71</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>92065</v>
+        <v>39499</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Augusto Monteiro</t>
+          <t>Isadora Nogueira</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Financeiro</t>
+          <t>P&amp;D</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -721,42 +721,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45086</v>
+        <v>45088</v>
       </c>
       <c r="G10" t="n">
-        <v>12409.29</v>
+        <v>4796.19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>35168</v>
+        <v>13583</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Thomas Campos</t>
+          <t>Lavínia Rezende</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jurídico</t>
+          <t>Financeiro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45100</v>
+        <v>45088</v>
       </c>
       <c r="G11" t="n">
-        <v>8589.5</v>
+        <v>5841.16</v>
       </c>
     </row>
   </sheetData>
